--- a/data/trans_orig/Viv_Temp_insuf-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Viv_Temp_insuf-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11246</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7081</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>16483</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>17,53%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>11,04%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>25,7%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>13119</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>7102</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>22301</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>17,9%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9,69%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>30,43%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>16560</t>
+          <t>8475</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10639</t>
+          <t>5034</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25945</t>
+          <t>13295</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>29678</t>
+          <t>19721</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20794</t>
+          <t>13787</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42958</t>
+          <t>26613</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>22,06%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>52899</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>47662</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>57064</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>82,47%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>74,3%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>88,96%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>60163</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>50981</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>66180</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>82,1%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>69,57%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>90,31%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>62806</t>
+          <t>48006</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53421</t>
+          <t>43186</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>68727</t>
+          <t>51447</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>122970</t>
+          <t>100905</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>109690</t>
+          <t>94013</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>131854</t>
+          <t>106839</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>88,57%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>17126</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>10654</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>24190</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>14,78%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>9,2%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>20,88%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>24787</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>12115</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>37101</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>19,42%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>9,49%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>29,06%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19056</t>
+          <t>22973</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12586</t>
+          <t>16009</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28717</t>
+          <t>30212</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>43844</t>
+          <t>40099</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>29642</t>
+          <t>30163</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>58109</t>
+          <t>51391</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>23,66%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>98709</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>91645</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>105181</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>85,22%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>79,12%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>90,8%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>111</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>102867</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>90553</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>115539</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>80,58%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>70,94%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>90,51%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>108540</t>
+          <t>78422</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>98879</t>
+          <t>71183</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>115010</t>
+          <t>85386</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>211406</t>
+          <t>177132</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>197141</t>
+          <t>165840</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>225608</t>
+          <t>187068</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>76,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>86,11%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>115835</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>115835</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>115835</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>142</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>127654</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>127654</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>127654</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>127596</t>
+          <t>101395</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>127596</t>
+          <t>101395</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>127596</t>
+          <t>101395</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>255250</t>
+          <t>217231</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>255250</t>
+          <t>217231</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>255250</t>
+          <t>217231</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>14479</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9642</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>19906</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>24,39%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>16,24%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>33,52%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>20568</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>15144</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>26416</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>35,3%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>25,99%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>45,33%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>16563</t>
+          <t>19771</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11394</t>
+          <t>14244</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23079</t>
+          <t>25323</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>37131</t>
+          <t>34250</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29559</t>
+          <t>26710</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46433</t>
+          <t>41735</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>36,0%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>44898</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>39471</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>49735</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>75,61%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>66,48%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>83,76%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>37700</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>31852</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>43124</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>64,7%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>54,67%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>74,01%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>50600</t>
+          <t>36787</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>44084</t>
+          <t>31235</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>55769</t>
+          <t>42314</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>65,04%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,64%</t>
+          <t>55,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>88300</t>
+          <t>81686</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>78998</t>
+          <t>74201</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>95872</t>
+          <t>89226</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>76,96%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>58268</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>58268</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>58268</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>56558</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>56558</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>56558</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>125431</t>
+          <t>115936</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>125431</t>
+          <t>115936</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>125431</t>
+          <t>115936</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>17701</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10040</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>27093</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>24,53%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>13,91%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>37,55%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>22077</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>15535</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>29242</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>31,93%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>22,47%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>42,29%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19199</t>
+          <t>21899</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10490</t>
+          <t>15458</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29370</t>
+          <t>29249</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>41276</t>
+          <t>39600</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28868</t>
+          <t>28778</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>52954</t>
+          <t>51243</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>36,1%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>54461</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>45069</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>62122</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>75,47%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>62,45%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>86,09%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>47067</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>39902</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>53609</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>68,07%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>57,71%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>77,53%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>58935</t>
+          <t>47869</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>48764</t>
+          <t>40519</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>67644</t>
+          <t>54310</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>58,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>106002</t>
+          <t>102330</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>94324</t>
+          <t>90687</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>118410</t>
+          <t>113152</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>72,1%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>79,72%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>72162</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>72162</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>72162</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>69144</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>69144</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>69144</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>78134</t>
+          <t>69768</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>78134</t>
+          <t>69768</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>78134</t>
+          <t>69768</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>147278</t>
+          <t>141930</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>147278</t>
+          <t>141930</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>147278</t>
+          <t>141930</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>11340</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>7334</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>16454</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>28,65%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>18,53%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>41,57%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>9815</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>6337</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>13987</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>28,44%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>18,36%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>40,53%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>12614</t>
+          <t>10312</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8395</t>
+          <t>6654</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17795</t>
+          <t>14755</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>22429</t>
+          <t>21652</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16908</t>
+          <t>16295</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28443</t>
+          <t>28089</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,36%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>28239</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>23125</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>32245</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>71,35%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>58,43%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>81,47%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>24698</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>20526</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>28176</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>71,56%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>59,47%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>81,64%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>28105</t>
+          <t>25296</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22924</t>
+          <t>20853</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32324</t>
+          <t>28954</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>81,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>52803</t>
+          <t>53535</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>46789</t>
+          <t>47098</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>58324</t>
+          <t>58892</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>71,2%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>78,33%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5436</t>
+          <t>4276</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2630</t>
+          <t>1927</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8930</t>
+          <t>7659</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>5273</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2494</t>
+          <t>2589</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8930</t>
+          <t>9216</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>10402</t>
+          <t>9549</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6384</t>
+          <t>5896</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15341</t>
+          <t>14534</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,46%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>44666</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>41283</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>47015</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>91,26%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>84,35%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>96,06%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>39996</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>36502</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>42802</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>88,04%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>80,34%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>94,21%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>51219</t>
+          <t>39777</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>47256</t>
+          <t>35834</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>53692</t>
+          <t>42461</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>91216</t>
+          <t>84443</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>86277</t>
+          <t>79458</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>95234</t>
+          <t>88096</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,73%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>45432</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>45432</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>45432</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45050</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45050</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45050</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>101618</t>
+          <t>93992</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>101618</t>
+          <t>93992</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>101618</t>
+          <t>93992</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>58695</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>47807</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>68375</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>41,8%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>34,05%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>48,7%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>46905</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>38128</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>57005</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>37,67%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>30,62%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>45,78%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>61870</t>
+          <t>46440</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>50229</t>
+          <t>36846</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>74349</t>
+          <t>55953</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>108775</t>
+          <t>105135</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>94194</t>
+          <t>91343</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>124683</t>
+          <t>118831</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>45,19%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>81716</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>72036</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>92604</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>58,2%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>51,3%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>65,95%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>77603</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>67503</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>86380</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>62,33%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>54,22%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>69,38%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>93199</t>
+          <t>76089</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>80720</t>
+          <t>66576</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>104840</t>
+          <t>85683</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>54,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>170802</t>
+          <t>157805</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>154894</t>
+          <t>144109</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>185383</t>
+          <t>171597</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>54,81%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>65,26%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>140411</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>140411</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>140411</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>176</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>124508</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>124508</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>124508</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>155069</t>
+          <t>122529</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>155069</t>
+          <t>122529</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>155069</t>
+          <t>122529</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>279577</t>
+          <t>262940</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>279577</t>
+          <t>262940</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>279577</t>
+          <t>262940</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3121,72 +3121,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>138872</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>131141</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>145639</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>87,11%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>82,26%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>91,36%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>170</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>116658</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>108121</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>121694</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>88,63%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>82,15%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>92,46%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>136422</t>
+          <t>124195</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>128198</t>
+          <t>114675</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>142259</t>
+          <t>129720</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>253080</t>
+          <t>263067</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>242454</t>
+          <t>252541</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>261914</t>
+          <t>273434</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>84,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>91,17%</t>
         </is>
       </c>
     </row>
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>20549</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>13782</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>28280</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>12,89%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>8,64%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>17,74%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>14961</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>9925</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>23498</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>11,37%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>7,54%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>17,85%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>20373</t>
+          <t>16302</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>14536</t>
+          <t>10777</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>28597</t>
+          <t>25822</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>35334</t>
+          <t>36851</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>26500</t>
+          <t>26484</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>45960</t>
+          <t>47377</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,8%</t>
         </is>
       </c>
     </row>
@@ -3347,57 +3347,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>159421</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>159421</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>159421</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>131619</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>131619</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>131619</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>156795</t>
+          <t>140497</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>156795</t>
+          <t>140497</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>156795</t>
+          <t>140497</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>288414</t>
+          <t>299918</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>288414</t>
+          <t>299918</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>288414</t>
+          <t>299918</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3464,72 +3464,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>374</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>273735</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>248371</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>297023</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>39,11%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>35,49%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>42,44%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>373</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>259364</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>227582</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>284129</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>39,04%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>34,25%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>42,76%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>374</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>287252</t>
+          <t>259338</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>263853</t>
+          <t>239667</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>314141</t>
+          <t>280734</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>546616</t>
+          <t>533073</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>503894</t>
+          <t>499121</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>581534</t>
+          <t>564113</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>42,49%</t>
         </is>
       </c>
     </row>
@@ -3577,72 +3577,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>602</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>426137</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>402849</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>451501</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>60,89%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>57,56%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>64,51%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>568</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>405057</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>380292</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>436839</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>60,96%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>57,24%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>65,75%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>602</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>473776</t>
+          <t>368549</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>446887</t>
+          <t>347153</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>497175</t>
+          <t>388220</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>55,29%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>878833</t>
+          <t>794686</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>843915</t>
+          <t>763646</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>921555</t>
+          <t>828638</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>57,51%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>62,41%</t>
         </is>
       </c>
     </row>
@@ -3690,57 +3690,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>941</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>664421</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>664421</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>664421</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>627887</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>627887</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>627887</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1425449</t>
+          <t>1327759</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1425449</t>
+          <t>1327759</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1425449</t>
+          <t>1327759</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
